--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.678</v>
+        <v>0.479</v>
       </c>
       <c r="E2">
-        <v>2.306</v>
+        <v>0.012</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,16 +600,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.006693267252876032</v>
+        <v>0.01404483734276689</v>
       </c>
       <c r="J2">
-        <v>0.005743392247033097</v>
+        <v>0.01139282566725407</v>
       </c>
       <c r="K2">
-        <v>351</v>
+        <v>43.1</v>
       </c>
       <c r="L2">
-        <v>0.5726872246696035</v>
+        <v>0.1132422490803994</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>740.4</v>
+        <v>790.4</v>
       </c>
       <c r="V2">
-        <v>0.1793821926105391</v>
+        <v>0.2280109620654839</v>
       </c>
       <c r="W2">
-        <v>1.975239167135622</v>
+        <v>0.07924250781393639</v>
       </c>
       <c r="X2">
-        <v>0.04498797543727869</v>
+        <v>0.09098825283628113</v>
       </c>
       <c r="Y2">
-        <v>1.930251191698343</v>
+        <v>-0.01174574502234474</v>
       </c>
       <c r="Z2">
-        <v>-128.1810639522927</v>
+        <v>0.9312848909767232</v>
       </c>
       <c r="AA2">
-        <v>-0.7361941289200515</v>
+        <v>0.01060996640944552</v>
       </c>
       <c r="AB2">
-        <v>0.0432604754529605</v>
+        <v>0.09509876185811728</v>
       </c>
       <c r="AC2">
-        <v>-0.7794546043730121</v>
+        <v>-0.08448879544867176</v>
       </c>
       <c r="AD2">
-        <v>599</v>
+        <v>1038.4</v>
       </c>
       <c r="AE2">
-        <v>14.2884825035614</v>
+        <v>14.0726745367146</v>
       </c>
       <c r="AF2">
-        <v>613.2884825035615</v>
+        <v>1052.472674536715</v>
       </c>
       <c r="AG2">
-        <v>-127.1115174964385</v>
+        <v>262.0726745367148</v>
       </c>
       <c r="AH2">
-        <v>0.1293642365119167</v>
+        <v>0.2329008715779885</v>
       </c>
       <c r="AI2">
-        <v>0.5302105897831253</v>
+        <v>0.6288026388219236</v>
       </c>
       <c r="AJ2">
-        <v>-0.03177479338628841</v>
+        <v>0.07028766700095983</v>
       </c>
       <c r="AK2">
-        <v>-0.3053447857408619</v>
+        <v>0.2966728336646353</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +690,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>86.06321839080459</v>
+        <v>127.2549019607843</v>
       </c>
       <c r="AP2">
-        <v>-18.26314906558025</v>
+        <v>32.11674933047975</v>
       </c>
     </row>
     <row r="3">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.678</v>
+        <v>0.479</v>
       </c>
       <c r="E3">
-        <v>2.306</v>
+        <v>0.012</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,16 +725,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.006693267252876032</v>
+        <v>0.01404483734276689</v>
       </c>
       <c r="J3">
-        <v>0.005743392247033097</v>
+        <v>0.01139282566725407</v>
       </c>
       <c r="K3">
-        <v>351</v>
+        <v>43.1</v>
       </c>
       <c r="L3">
-        <v>0.5726872246696035</v>
+        <v>0.1132422490803994</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>740.4</v>
+        <v>790.4</v>
       </c>
       <c r="V3">
-        <v>0.1793821926105391</v>
+        <v>0.2280109620654839</v>
       </c>
       <c r="W3">
-        <v>1.975239167135622</v>
+        <v>0.07924250781393639</v>
       </c>
       <c r="X3">
-        <v>0.04498797543727869</v>
+        <v>0.09098825283628113</v>
       </c>
       <c r="Y3">
-        <v>1.930251191698343</v>
+        <v>-0.01174574502234474</v>
       </c>
       <c r="Z3">
-        <v>-128.1810639522927</v>
+        <v>0.9312848909767232</v>
       </c>
       <c r="AA3">
-        <v>-0.7361941289200515</v>
+        <v>0.01060996640944552</v>
       </c>
       <c r="AB3">
-        <v>0.0432604754529605</v>
+        <v>0.09509876185811728</v>
       </c>
       <c r="AC3">
-        <v>-0.7794546043730121</v>
+        <v>-0.08448879544867176</v>
       </c>
       <c r="AD3">
-        <v>599</v>
+        <v>1038.4</v>
       </c>
       <c r="AE3">
-        <v>14.2884825035614</v>
+        <v>14.0726745367146</v>
       </c>
       <c r="AF3">
-        <v>613.2884825035615</v>
+        <v>1052.472674536715</v>
       </c>
       <c r="AG3">
-        <v>-127.1115174964385</v>
+        <v>262.0726745367148</v>
       </c>
       <c r="AH3">
-        <v>0.1293642365119167</v>
+        <v>0.2329008715779885</v>
       </c>
       <c r="AI3">
-        <v>0.5302105897831253</v>
+        <v>0.6288026388219236</v>
       </c>
       <c r="AJ3">
-        <v>-0.03177479338628841</v>
+        <v>0.07028766700095983</v>
       </c>
       <c r="AK3">
-        <v>-0.3053447857408619</v>
+        <v>0.2966728336646353</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>86.06321839080459</v>
+        <v>127.2549019607843</v>
       </c>
       <c r="AP3">
-        <v>-18.26314906558025</v>
+        <v>32.11674933047975</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_brokerage_investment_banking.xlsx
@@ -588,10 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.479</v>
-      </c>
-      <c r="E2">
-        <v>0.012</v>
+        <v>1.11</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,16 +597,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.01404483734276689</v>
+        <v>0.004553922992712212</v>
       </c>
       <c r="J2">
-        <v>0.01139282566725407</v>
+        <v>0.003792044871165575</v>
       </c>
       <c r="K2">
-        <v>43.1</v>
+        <v>301.8</v>
       </c>
       <c r="L2">
-        <v>0.1132422490803994</v>
+        <v>0.3900232618247609</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +630,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>790.4</v>
+        <v>463.9</v>
       </c>
       <c r="V2">
-        <v>0.2280109620654839</v>
+        <v>0.09630875269888722</v>
       </c>
       <c r="W2">
-        <v>0.07924250781393639</v>
+        <v>0.4795042897998094</v>
       </c>
       <c r="X2">
-        <v>0.09098825283628113</v>
+        <v>0.08091789095882657</v>
       </c>
       <c r="Y2">
-        <v>-0.01174574502234474</v>
+        <v>0.3985863988409828</v>
       </c>
       <c r="Z2">
-        <v>0.9312848909767232</v>
+        <v>0.862344813540355</v>
       </c>
       <c r="AA2">
-        <v>0.01060996640944552</v>
+        <v>0.003270050227361937</v>
       </c>
       <c r="AB2">
-        <v>0.09509876185811728</v>
+        <v>0.08412914973344698</v>
       </c>
       <c r="AC2">
-        <v>-0.08448879544867176</v>
+        <v>-0.08085909950608505</v>
       </c>
       <c r="AD2">
-        <v>1038.4</v>
+        <v>2819.9</v>
       </c>
       <c r="AE2">
-        <v>14.0726745367146</v>
+        <v>29.43087194119645</v>
       </c>
       <c r="AF2">
-        <v>1052.472674536715</v>
+        <v>2849.330871941197</v>
       </c>
       <c r="AG2">
-        <v>262.0726745367148</v>
+        <v>2385.430871941197</v>
       </c>
       <c r="AH2">
-        <v>0.2329008715779885</v>
+        <v>0.3716778280383957</v>
       </c>
       <c r="AI2">
-        <v>0.6288026388219236</v>
+        <v>0.7570495789651438</v>
       </c>
       <c r="AJ2">
-        <v>0.07028766700095983</v>
+        <v>0.3312072209784991</v>
       </c>
       <c r="AK2">
-        <v>0.2966728336646353</v>
+        <v>0.7228948890153014</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -690,10 +687,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>127.2549019607843</v>
+        <v>299.6705632306058</v>
       </c>
       <c r="AP2">
-        <v>32.11674933047975</v>
+        <v>253.499561311498</v>
       </c>
     </row>
     <row r="3">
@@ -713,10 +710,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.479</v>
-      </c>
-      <c r="E3">
-        <v>0.012</v>
+        <v>1.11</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,16 +719,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.01404483734276689</v>
+        <v>0.004553922992712212</v>
       </c>
       <c r="J3">
-        <v>0.01139282566725407</v>
+        <v>0.003792044871165575</v>
       </c>
       <c r="K3">
-        <v>43.1</v>
+        <v>301.8</v>
       </c>
       <c r="L3">
-        <v>0.1132422490803994</v>
+        <v>0.3900232618247609</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>790.4</v>
+        <v>463.9</v>
       </c>
       <c r="V3">
-        <v>0.2280109620654839</v>
+        <v>0.09630875269888722</v>
       </c>
       <c r="W3">
-        <v>0.07924250781393639</v>
+        <v>0.4795042897998094</v>
       </c>
       <c r="X3">
-        <v>0.09098825283628113</v>
+        <v>0.08091789095882657</v>
       </c>
       <c r="Y3">
-        <v>-0.01174574502234474</v>
+        <v>0.3985863988409828</v>
       </c>
       <c r="Z3">
-        <v>0.9312848909767232</v>
+        <v>0.862344813540355</v>
       </c>
       <c r="AA3">
-        <v>0.01060996640944552</v>
+        <v>0.003270050227361937</v>
       </c>
       <c r="AB3">
-        <v>0.09509876185811728</v>
+        <v>0.08412914973344698</v>
       </c>
       <c r="AC3">
-        <v>-0.08448879544867176</v>
+        <v>-0.08085909950608505</v>
       </c>
       <c r="AD3">
-        <v>1038.4</v>
+        <v>2819.9</v>
       </c>
       <c r="AE3">
-        <v>14.0726745367146</v>
+        <v>29.43087194119645</v>
       </c>
       <c r="AF3">
-        <v>1052.472674536715</v>
+        <v>2849.330871941197</v>
       </c>
       <c r="AG3">
-        <v>262.0726745367148</v>
+        <v>2385.430871941197</v>
       </c>
       <c r="AH3">
-        <v>0.2329008715779885</v>
+        <v>0.3716778280383957</v>
       </c>
       <c r="AI3">
-        <v>0.6288026388219236</v>
+        <v>0.7570495789651438</v>
       </c>
       <c r="AJ3">
-        <v>0.07028766700095983</v>
+        <v>0.3312072209784991</v>
       </c>
       <c r="AK3">
-        <v>0.2966728336646353</v>
+        <v>0.7228948890153014</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>127.2549019607843</v>
+        <v>299.6705632306058</v>
       </c>
       <c r="AP3">
-        <v>32.11674933047975</v>
+        <v>253.499561311498</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_brokerage_investment_banking.xlsx
@@ -588,7 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.11</v>
+        <v>0.6759999999999999</v>
+      </c>
+      <c r="E2">
+        <v>0.64</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -597,16 +600,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.004553922992712212</v>
+        <v>0.003494357031729296</v>
       </c>
       <c r="J2">
-        <v>0.003792044871165575</v>
+        <v>0.003079051522261728</v>
       </c>
       <c r="K2">
-        <v>301.8</v>
+        <v>340.6</v>
       </c>
       <c r="L2">
-        <v>0.3900232618247609</v>
+        <v>0.2606765651308741</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>463.9</v>
+        <v>569.2</v>
       </c>
       <c r="V2">
-        <v>0.09630875269888722</v>
+        <v>0.07185598505314718</v>
       </c>
       <c r="W2">
-        <v>0.4795042897998094</v>
+        <v>0.3738338272417956</v>
       </c>
       <c r="X2">
-        <v>0.08091789095882657</v>
+        <v>0.07812752152627758</v>
       </c>
       <c r="Y2">
-        <v>0.3985863988409828</v>
+        <v>0.295706305715518</v>
       </c>
       <c r="Z2">
-        <v>0.862344813540355</v>
+        <v>0.4020714260114899</v>
       </c>
       <c r="AA2">
-        <v>0.003270050227361937</v>
+        <v>0.001237998636318622</v>
       </c>
       <c r="AB2">
-        <v>0.08412914973344698</v>
+        <v>0.07987308101558876</v>
       </c>
       <c r="AC2">
-        <v>-0.08085909950608505</v>
+        <v>-0.07863508237927014</v>
       </c>
       <c r="AD2">
-        <v>2819.9</v>
+        <v>2851.5</v>
       </c>
       <c r="AE2">
-        <v>29.43087194119645</v>
+        <v>34.17136551171252</v>
       </c>
       <c r="AF2">
-        <v>2849.330871941197</v>
+        <v>2885.671365511712</v>
       </c>
       <c r="AG2">
-        <v>2385.430871941197</v>
+        <v>2316.471365511712</v>
       </c>
       <c r="AH2">
-        <v>0.3716778280383957</v>
+        <v>0.2670169621272855</v>
       </c>
       <c r="AI2">
-        <v>0.7570495789651438</v>
+        <v>0.6955316545842823</v>
       </c>
       <c r="AJ2">
-        <v>0.3312072209784991</v>
+        <v>0.2262649414911778</v>
       </c>
       <c r="AK2">
-        <v>0.7228948890153014</v>
+        <v>0.6471184443995948</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -687,10 +690,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>299.6705632306058</v>
+        <v>250.1315789473684</v>
       </c>
       <c r="AP2">
-        <v>253.499561311498</v>
+        <v>203.1992425887467</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.11</v>
+        <v>0.6759999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.64</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -719,16 +725,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.004553922992712212</v>
+        <v>0.003494357031729296</v>
       </c>
       <c r="J3">
-        <v>0.003792044871165575</v>
+        <v>0.003079051522261728</v>
       </c>
       <c r="K3">
-        <v>301.8</v>
+        <v>340.6</v>
       </c>
       <c r="L3">
-        <v>0.3900232618247609</v>
+        <v>0.2606765651308741</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>463.9</v>
+        <v>569.2</v>
       </c>
       <c r="V3">
-        <v>0.09630875269888722</v>
+        <v>0.07185598505314718</v>
       </c>
       <c r="W3">
-        <v>0.4795042897998094</v>
+        <v>0.3738338272417956</v>
       </c>
       <c r="X3">
-        <v>0.08091789095882657</v>
+        <v>0.07812752152627758</v>
       </c>
       <c r="Y3">
-        <v>0.3985863988409828</v>
+        <v>0.295706305715518</v>
       </c>
       <c r="Z3">
-        <v>0.862344813540355</v>
+        <v>0.4020714260114899</v>
       </c>
       <c r="AA3">
-        <v>0.003270050227361937</v>
+        <v>0.001237998636318622</v>
       </c>
       <c r="AB3">
-        <v>0.08412914973344698</v>
+        <v>0.07987308101558876</v>
       </c>
       <c r="AC3">
-        <v>-0.08085909950608505</v>
+        <v>-0.07863508237927014</v>
       </c>
       <c r="AD3">
-        <v>2819.9</v>
+        <v>2851.5</v>
       </c>
       <c r="AE3">
-        <v>29.43087194119645</v>
+        <v>34.17136551171252</v>
       </c>
       <c r="AF3">
-        <v>2849.330871941197</v>
+        <v>2885.671365511712</v>
       </c>
       <c r="AG3">
-        <v>2385.430871941197</v>
+        <v>2316.471365511712</v>
       </c>
       <c r="AH3">
-        <v>0.3716778280383957</v>
+        <v>0.2670169621272855</v>
       </c>
       <c r="AI3">
-        <v>0.7570495789651438</v>
+        <v>0.6955316545842823</v>
       </c>
       <c r="AJ3">
-        <v>0.3312072209784991</v>
+        <v>0.2262649414911778</v>
       </c>
       <c r="AK3">
-        <v>0.7228948890153014</v>
+        <v>0.6471184443995948</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -809,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>299.6705632306058</v>
+        <v>250.1315789473684</v>
       </c>
       <c r="AP3">
-        <v>253.499561311498</v>
+        <v>203.1992425887467</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_brokerage_investment_banking.xlsx
@@ -642,10 +642,10 @@
         <v>0.3738338272417956</v>
       </c>
       <c r="X2">
-        <v>0.07812752152627758</v>
+        <v>0.07811877494775712</v>
       </c>
       <c r="Y2">
-        <v>0.295706305715518</v>
+        <v>0.2957150522940385</v>
       </c>
       <c r="Z2">
         <v>0.4020714260114899</v>
@@ -654,10 +654,10 @@
         <v>0.001237998636318622</v>
       </c>
       <c r="AB2">
-        <v>0.07987308101558876</v>
+        <v>0.07986666992189384</v>
       </c>
       <c r="AC2">
-        <v>-0.07863508237927014</v>
+        <v>-0.07862867128557521</v>
       </c>
       <c r="AD2">
         <v>2851.5</v>
@@ -767,10 +767,10 @@
         <v>0.3738338272417956</v>
       </c>
       <c r="X3">
-        <v>0.07812752152627758</v>
+        <v>0.07811877494775712</v>
       </c>
       <c r="Y3">
-        <v>0.295706305715518</v>
+        <v>0.2957150522940385</v>
       </c>
       <c r="Z3">
         <v>0.4020714260114899</v>
@@ -779,10 +779,10 @@
         <v>0.001237998636318622</v>
       </c>
       <c r="AB3">
-        <v>0.07987308101558876</v>
+        <v>0.07986666992189384</v>
       </c>
       <c r="AC3">
-        <v>-0.07863508237927014</v>
+        <v>-0.07862867128557521</v>
       </c>
       <c r="AD3">
         <v>2851.5</v>
